--- a/manuscript/tables/e-table-2-key-variables.xlsx
+++ b/manuscript/tables/e-table-2-key-variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/Gwen's Documents/Work/Boston University GRA/Projects/GLP1s for AD/03_analysis/repository/newer-glp1-dementia-repkit/manuscript/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/Gwen's Documents/Work/Boston University GRA/Projects/GLP1s for AD/03_analysis/newer-glp1-dementia-repkit/manuscript/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90010B0-A8C0-B247-A262-93B6E8948999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837CE96B-C73E-8B42-A707-018D29C38640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16180" windowHeight="21600" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Key Variables" sheetId="1" r:id="rId1"/>

--- a/manuscript/tables/e-table-2-key-variables.xlsx
+++ b/manuscript/tables/e-table-2-key-variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/Gwen's Documents/Work/Boston University GRA/Projects/GLP1s for AD/03_analysis/newer-glp1-dementia-repkit/manuscript/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837CE96B-C73E-8B42-A707-018D29C38640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5E2C6A-4184-D042-8CEA-DE0DE1AFE958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
   </bookViews>
   <sheets>
     <sheet name="Key Variables" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="152">
   <si>
     <t>Variable</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Gastroparesis</t>
   </si>
   <si>
-    <t>Appendicitis</t>
-  </si>
-  <si>
     <t>Traumatic tooth fracture</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Basal cell carcinoma</t>
   </si>
   <si>
-    <t>K35</t>
-  </si>
-  <si>
     <t>Comorbidities</t>
   </si>
   <si>
@@ -176,12 +170,6 @@
     <t>Peripheral vascular disease</t>
   </si>
   <si>
-    <t>Ventricular heart disease</t>
-  </si>
-  <si>
-    <t>I42, I43, I51.4</t>
-  </si>
-  <si>
     <t>Edema</t>
   </si>
   <si>
@@ -324,13 +312,196 @@
   </si>
   <si>
     <t>C0-C9</t>
+  </si>
+  <si>
+    <t>Neurocognitive examination</t>
+  </si>
+  <si>
+    <t>96116, 96132, 96133, 96118, 96119, 96120, 96136, 96137, 96138, 96139, 96146</t>
+  </si>
+  <si>
+    <t>Immunization visit</t>
+  </si>
+  <si>
+    <t>Z23</t>
+  </si>
+  <si>
+    <t>Cancer screening visit</t>
+  </si>
+  <si>
+    <t>Z12</t>
+  </si>
+  <si>
+    <t>General health examination</t>
+  </si>
+  <si>
+    <t>Z00</t>
+  </si>
+  <si>
+    <t>Anemia</t>
+  </si>
+  <si>
+    <t>D50, D52-D53, D62-D64</t>
+  </si>
+  <si>
+    <t>Arthropathies</t>
+  </si>
+  <si>
+    <t>M05-M06, M15-M19</t>
+  </si>
+  <si>
+    <t>Atrial fibrillation and other arrhythmias</t>
+  </si>
+  <si>
+    <t>I47-I49</t>
+  </si>
+  <si>
+    <t>Contusion/superficial injury</t>
+  </si>
+  <si>
+    <t>S00, S10, S20, S30, S40, S50, S60, S70, S80-S81, S90-S91</t>
+  </si>
+  <si>
+    <t>Debility, weakness, failure to thrive</t>
+  </si>
+  <si>
+    <t>R531, R5381, R54, R627, R64</t>
+  </si>
+  <si>
+    <t>Dehydration and electrolyte disorders</t>
+  </si>
+  <si>
+    <t>E86-E87</t>
+  </si>
+  <si>
+    <t>Delirium and other organic mental disorders</t>
+  </si>
+  <si>
+    <t>F05-F06</t>
+  </si>
+  <si>
+    <t>Dorsopathies</t>
+  </si>
+  <si>
+    <t>M40-M43, M45-M51, M53-M54</t>
+  </si>
+  <si>
+    <t>Falls, gait and mobility problems</t>
+  </si>
+  <si>
+    <t>R26, R296, Z9181, W00-W01, W03-W19</t>
+  </si>
+  <si>
+    <t>Osteoporosis</t>
+  </si>
+  <si>
+    <t>M81</t>
+  </si>
+  <si>
+    <t>Parkinson's and related disorders</t>
+  </si>
+  <si>
+    <t>G20-G21, G23</t>
+  </si>
+  <si>
+    <t>Pneumonia and influenza</t>
+  </si>
+  <si>
+    <t>J09-J18</t>
+  </si>
+  <si>
+    <t>Sepsis and serious bacterial infections</t>
+  </si>
+  <si>
+    <t>A40-A41, R652</t>
+  </si>
+  <si>
+    <t>Serious mental illness</t>
+  </si>
+  <si>
+    <t>F20-F25, F28-F31</t>
+  </si>
+  <si>
+    <t>Skin infections and ulcers</t>
+  </si>
+  <si>
+    <t>E11621, L00-L05, L08, L89, L97</t>
+  </si>
+  <si>
+    <t>Smoking</t>
+  </si>
+  <si>
+    <t>F17, Z720, Z87891</t>
+  </si>
+  <si>
+    <t>Syncope and hypotension</t>
+  </si>
+  <si>
+    <t>I95, R55</t>
+  </si>
+  <si>
+    <t>Valvular heart disease</t>
+  </si>
+  <si>
+    <t>Venous thromboembolism</t>
+  </si>
+  <si>
+    <t>I26, I80-I82</t>
+  </si>
+  <si>
+    <t>Herpes zoster</t>
+  </si>
+  <si>
+    <t>V00-V99</t>
+  </si>
+  <si>
+    <t>B020-B029</t>
+  </si>
+  <si>
+    <t>Chornic lower respiratory diseases</t>
+  </si>
+  <si>
+    <t>Hearing loss</t>
+  </si>
+  <si>
+    <t>Lens disorders</t>
+  </si>
+  <si>
+    <t>H90, H91</t>
+  </si>
+  <si>
+    <t>J40-H47</t>
+  </si>
+  <si>
+    <t>H25-H28</t>
+  </si>
+  <si>
+    <t>Positive control outcomes</t>
+  </si>
+  <si>
+    <t>Gastrointestinal events</t>
+  </si>
+  <si>
+    <t>Transport accident (inpatient only)</t>
+  </si>
+  <si>
+    <t>R11, R12, R14, K590, K30, K3184, K21, K85, K861, K197, K5289, K529</t>
+  </si>
+  <si>
+    <t>I05, I07, I08, I091, I0989, I34-I39, Q230, Q232, Q233</t>
+  </si>
+  <si>
+    <t>Cardiomyopathy and myocarditis</t>
+  </si>
+  <si>
+    <t>I40-I43, I514</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -357,6 +528,18 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -378,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -389,11 +572,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -522,13 +716,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}" name="Table1" displayName="Table1" ref="A1:D47" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D47" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}" name="Table1" displayName="Table1" ref="A1:D76" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:D76" xr:uid="{46DFB6FE-86CF-6D4B-9506-95A0A653C31E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D76">
+    <sortCondition ref="B1:B76"/>
+  </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B0B29E94-BFDD-3C42-8ED5-F78E5C6AF6E7}" name="Step" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{05D7060B-B93D-CA4E-B901-F6FFF18D12B3}" name="Variable" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{9552CCFC-80DF-474E-B509-DF09D3C8531C}" name="ICD-10 Codes" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{EE8F03F1-C212-DA43-8153-9A51B62EAFB2}" name="CPT Codes" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B0B29E94-BFDD-3C42-8ED5-F78E5C6AF6E7}" name="Step" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{05D7060B-B93D-CA4E-B901-F6FFF18D12B3}" name="Variable" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{9552CCFC-80DF-474E-B509-DF09D3C8531C}" name="ICD-10 Codes" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{EE8F03F1-C212-DA43-8153-9A51B62EAFB2}" name="CPT Codes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -849,9 +1046,29 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
+  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BBE2C8-ED3D-B242-85C9-E05BBE5783B0}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.83203125" style="1" customWidth="1"/>
@@ -861,7 +1078,7 @@
     <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -872,471 +1089,720 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
+    </row>
+    <row r="5" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="2" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="2" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" ht="136" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" ht="289" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" ht="119" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" ht="136" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="289" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63" spans="1:4" ht="119" x14ac:dyDescent="0.2">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D73" s="2"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F77" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="F73:F77">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
